--- a/samples/Sample_6_For_Individual_UPSC_Aspirant.xlsx
+++ b/samples/Sample_6_For_Individual_UPSC_Aspirant.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karthik Kumar</t>
+          <t>Vivaan Patel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
         <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1134,22 +1134,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D2" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Great turnaround this term, keep the momentum going!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1224,21 +1228,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C2" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Optional Paper 2 Topics</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1314,28 +1322,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="C2" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D2" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Environment</t>
+          <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Encouraging progress, on the right track now.</t>
         </is>
       </c>
     </row>

--- a/samples/Sample_6_For_Individual_UPSC_Aspirant.xlsx
+++ b/samples/Sample_6_For_Individual_UPSC_Aspirant.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prelims Mock 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prelims Mock 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mains Mock 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mains Mock 2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE2027-Prelims Mock 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE2027-Prelims Mock 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE2027-Mains Mock 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSE2027-Mains Mock 2" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -470,7 +470,6 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -478,7 +477,6 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -486,7 +484,6 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -513,7 +510,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -533,7 +529,6 @@
           <t>Teacher Name</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -605,7 +600,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prelims Mock 1</t>
+          <t>CSE2027-Prelims Mock 1</t>
         </is>
       </c>
     </row>
@@ -664,7 +659,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prelims Mock 2</t>
+          <t>CSE2027-Prelims Mock 2</t>
         </is>
       </c>
     </row>
@@ -723,7 +718,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mains Mock 1</t>
+          <t>CSE2027-Mains Mock 1</t>
         </is>
       </c>
     </row>
@@ -782,7 +777,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mains Mock 2</t>
+          <t>CSE2027-Mains Mock 2</t>
         </is>
       </c>
     </row>
@@ -1058,8 +1053,6 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1148,7 +1141,6 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -1247,7 +1239,6 @@
           <t>Optional Paper 2 Topics</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
